--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_store_gashaponmachine_info[商店-扭蛋机].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_store_gashaponmachine_info[商店-扭蛋机].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="StoreGashaponMachineInfo" sheetId="1" r:id="rId1"/>
@@ -77,7 +77,7 @@
     <t>内容</t>
   </si>
   <si>
-    <t>解锁ID</t>
+    <t>解锁ID用,分割</t>
   </si>
   <si>
     <t>名字</t>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_store_gashaponmachine_info[商店-扭蛋机].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_store_gashaponmachine_info[商店-扭蛋机].xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Unity\DemonLordRoguelike\Demon Lord Roguelike\Assets\Data\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17655"/>
   </bookViews>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_store_gashaponmachine_info[商店-扭蛋机].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_store_gashaponmachine_info[商店-扭蛋机].xlsx
@@ -1385,7 +1385,7 @@
         <v>1</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E10" s="0" t="inlineStr">
         <is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_store_gashaponmachine_info[商店-扭蛋机].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_store_gashaponmachine_info[商店-扭蛋机].xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H114"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="52.625" customWidth="1" style="1" min="2" max="2"/>
@@ -1276,601 +1276,3472 @@
     </row>
     <row r="7">
       <c r="A7" s="0" t="n">
-        <v>20001</v>
+        <v>10011</v>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t>2001-2004</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="C7" s="0" t="n">
         <v>1</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="E7" s="0" t="inlineStr">
         <is>
-          <t>ui_research_35,Research</t>
-        </is>
-      </c>
-      <c r="F7" s="0" t="inlineStr">
-        <is>
-          <t>300200000,300200001|300200002|300200003|300200004|</t>
-        </is>
+          <t>ui_class_3</t>
+        </is>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>300110011</v>
       </c>
       <c r="G7" s="0" t="n">
-        <v>20001</v>
+        <v>10011</v>
       </c>
       <c r="H7" s="0" t="inlineStr">
         <is>
-          <t>骷髅</t>
+          <t>人类战士x1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="n">
-        <v>20002</v>
+        <v>10012</v>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t>2001-2004</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="C8" s="0" t="n">
         <v>5</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="E8" s="0" t="inlineStr">
         <is>
-          <t>ui_research_35,Research</t>
+          <t>ui_class_3</t>
         </is>
       </c>
       <c r="F8" s="0" t="n">
-        <v>300200101</v>
+        <v>300110012</v>
       </c>
       <c r="G8" s="0" t="n">
-        <v>20002</v>
+        <v>10012</v>
       </c>
       <c r="H8" s="0" t="inlineStr">
         <is>
-          <t>骷髅x5</t>
+          <t>人类战士x5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="n">
-        <v>20003</v>
+        <v>10013</v>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t>2001-2004</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="C9" s="0" t="n">
         <v>10</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>100</v>
+        <v>2000</v>
       </c>
       <c r="E9" s="0" t="inlineStr">
         <is>
-          <t>ui_research_35,Research</t>
+          <t>ui_class_3</t>
         </is>
       </c>
       <c r="F9" s="0" t="n">
-        <v>300200102</v>
+        <v>300110013</v>
       </c>
       <c r="G9" s="0" t="n">
-        <v>20003</v>
+        <v>10013</v>
       </c>
       <c r="H9" s="0" t="inlineStr">
         <is>
-          <t>骷髅x10</t>
+          <t>人类战士x10</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="n">
-        <v>30001</v>
+        <v>10021</v>
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t>3001-3004</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="C10" s="0" t="n">
         <v>1</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="E10" s="0" t="inlineStr">
         <is>
-          <t>ui_research_37,Research</t>
-        </is>
-      </c>
-      <c r="F10" s="0" t="inlineStr">
-        <is>
-          <t>300300000,300300001|300300002|300300003|300300004|</t>
-        </is>
+          <t>ui_class_6</t>
+        </is>
+      </c>
+      <c r="F10" s="0" t="n">
+        <v>300110021</v>
       </c>
       <c r="G10" s="0" t="n">
-        <v>30001</v>
+        <v>10021</v>
       </c>
       <c r="H10" s="0" t="inlineStr">
         <is>
-          <t>史莱姆</t>
+          <t>人类弓箭手x1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="n">
-        <v>30002</v>
+        <v>10022</v>
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t>3001-3004</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="C11" s="0" t="n">
         <v>5</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="E11" s="0" t="inlineStr">
         <is>
-          <t>ui_research_37,Research</t>
+          <t>ui_class_6</t>
         </is>
       </c>
       <c r="F11" s="0" t="n">
-        <v>300300101</v>
+        <v>300110022</v>
       </c>
       <c r="G11" s="0" t="n">
-        <v>30002</v>
+        <v>10022</v>
       </c>
       <c r="H11" s="0" t="inlineStr">
         <is>
-          <t>史莱姆x5</t>
+          <t>人类弓箭手x5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="n">
-        <v>30003</v>
+        <v>10023</v>
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t>3001-3004</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="C12" s="0" t="n">
         <v>10</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>400</v>
+        <v>2000</v>
       </c>
       <c r="E12" s="0" t="inlineStr">
         <is>
-          <t>ui_research_37,Research</t>
+          <t>ui_class_6</t>
         </is>
       </c>
       <c r="F12" s="0" t="n">
-        <v>300300102</v>
+        <v>300110023</v>
       </c>
       <c r="G12" s="0" t="n">
-        <v>30003</v>
+        <v>10023</v>
       </c>
       <c r="H12" s="0" t="inlineStr">
         <is>
-          <t>史莱姆x10</t>
+          <t>人类弓箭手x10</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="n">
-        <v>40001</v>
+        <v>10031</v>
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t>4001-4005</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="C13" s="0" t="n">
         <v>1</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="E13" s="0" t="inlineStr">
         <is>
-          <t>ui_research_41,Research</t>
-        </is>
-      </c>
-      <c r="F13" s="0" t="inlineStr">
-        <is>
-          <t>300400000,300400001|300400002|300400003|300400004|300400005|</t>
-        </is>
+          <t>ui_class_10</t>
+        </is>
+      </c>
+      <c r="F13" s="0" t="n">
+        <v>300110031</v>
       </c>
       <c r="G13" s="0" t="n">
-        <v>40001</v>
+        <v>10031</v>
       </c>
       <c r="H13" s="0" t="inlineStr">
         <is>
-          <t>魅魔</t>
+          <t>人类魔法师（火）x1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="n">
-        <v>40002</v>
+        <v>10032</v>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>4001-4005</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="C14" s="0" t="n">
         <v>5</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="E14" s="0" t="inlineStr">
         <is>
-          <t>ui_research_41,Research</t>
+          <t>ui_class_10</t>
         </is>
       </c>
       <c r="F14" s="0" t="n">
-        <v>300400101</v>
+        <v>300110032</v>
       </c>
       <c r="G14" s="0" t="n">
-        <v>40002</v>
+        <v>10032</v>
       </c>
       <c r="H14" s="0" t="inlineStr">
         <is>
-          <t>魅魔x5</t>
+          <t>人类魔法师（火）x5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="n">
-        <v>40003</v>
+        <v>10033</v>
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t>4001-4005</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="C15" s="0" t="n">
         <v>10</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="E15" s="0" t="inlineStr">
         <is>
-          <t>ui_research_41,Research</t>
+          <t>ui_class_10</t>
         </is>
       </c>
       <c r="F15" s="0" t="n">
-        <v>300400102</v>
+        <v>300110033</v>
       </c>
       <c r="G15" s="0" t="n">
-        <v>40003</v>
+        <v>10033</v>
       </c>
       <c r="H15" s="0" t="inlineStr">
         <is>
-          <t>魅魔x10</t>
+          <t>人类魔法师（火）x10</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="n">
-        <v>50001</v>
+        <v>10041</v>
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t>5001-5004</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="C16" s="0" t="n">
         <v>1</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="E16" s="0" t="inlineStr">
         <is>
-          <t>ui_research_40,Research</t>
-        </is>
-      </c>
-      <c r="F16" s="0" t="inlineStr">
-        <is>
-          <t>300500000,300500001|300500002|300500003|300500004|</t>
-        </is>
+          <t>ui_class_2</t>
+        </is>
+      </c>
+      <c r="F16" s="0" t="n">
+        <v>300110041</v>
       </c>
       <c r="G16" s="0" t="n">
-        <v>50001</v>
+        <v>10041</v>
       </c>
       <c r="H16" s="0" t="inlineStr">
         <is>
-          <t>牛头人</t>
+          <t>人类魔法师（冰）x1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="n">
-        <v>50002</v>
+        <v>10042</v>
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t>5001-5004</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="C17" s="0" t="n">
         <v>5</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="E17" s="0" t="inlineStr">
         <is>
-          <t>ui_research_40,Research</t>
+          <t>ui_class_2</t>
         </is>
       </c>
       <c r="F17" s="0" t="n">
-        <v>300500101</v>
+        <v>300110042</v>
       </c>
       <c r="G17" s="0" t="n">
-        <v>50002</v>
+        <v>10042</v>
       </c>
       <c r="H17" s="0" t="inlineStr">
         <is>
-          <t>牛头人x5</t>
+          <t>人类魔法师（冰）x5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="n">
-        <v>50003</v>
+        <v>10043</v>
       </c>
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t>5001-5004</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="C18" s="0" t="n">
         <v>10</v>
       </c>
       <c r="D18" s="0" t="n">
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="E18" s="0" t="inlineStr">
         <is>
-          <t>ui_research_40,Research</t>
+          <t>ui_class_2</t>
         </is>
       </c>
       <c r="F18" s="0" t="n">
-        <v>300500102</v>
+        <v>300110043</v>
       </c>
       <c r="G18" s="0" t="n">
-        <v>50003</v>
+        <v>10043</v>
       </c>
       <c r="H18" s="0" t="inlineStr">
         <is>
-          <t>牛头人x10</t>
+          <t>人类魔法师（冰）x10</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="n">
-        <v>60001</v>
+        <v>20001</v>
       </c>
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t>6001-6005</t>
+          <t>2001-2004</t>
         </is>
       </c>
       <c r="C19" s="0" t="n">
         <v>1</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E19" s="0" t="inlineStr">
         <is>
-          <t>ui_research_39,Research</t>
+          <t>ui_research_35,Research</t>
         </is>
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
-          <t>300600000,300600001|300600002|300600003|300600004|300600005|</t>
+          <t>300200000,300200001|300200002|300200003|300200004|</t>
         </is>
       </c>
       <c r="G19" s="0" t="n">
-        <v>60001</v>
+        <v>20001</v>
       </c>
       <c r="H19" s="0" t="inlineStr">
         <is>
-          <t>哥布林</t>
+          <t>骷髅</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="n">
-        <v>60002</v>
+        <v>20002</v>
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t>6001-6005</t>
+          <t>2001-2004</t>
         </is>
       </c>
       <c r="C20" s="0" t="n">
         <v>5</v>
       </c>
       <c r="D20" s="0" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E20" s="0" t="inlineStr">
         <is>
-          <t>ui_research_39,Research</t>
+          <t>ui_research_35,Research</t>
         </is>
       </c>
       <c r="F20" s="0" t="n">
-        <v>300600101</v>
+        <v>300200101</v>
       </c>
       <c r="G20" s="0" t="n">
-        <v>60002</v>
+        <v>20002</v>
       </c>
       <c r="H20" s="0" t="inlineStr">
         <is>
-          <t>哥布林x5</t>
+          <t>骷髅x5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="n">
-        <v>60003</v>
+        <v>20003</v>
       </c>
       <c r="B21" s="0" t="inlineStr">
         <is>
-          <t>6001-6005</t>
+          <t>2001-2004</t>
         </is>
       </c>
       <c r="C21" s="0" t="n">
         <v>10</v>
       </c>
       <c r="D21" s="0" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E21" s="0" t="inlineStr">
         <is>
-          <t>ui_research_39,Research</t>
+          <t>ui_research_35,Research</t>
         </is>
       </c>
       <c r="F21" s="0" t="n">
-        <v>300600102</v>
+        <v>300200102</v>
       </c>
       <c r="G21" s="0" t="n">
-        <v>60003</v>
+        <v>20003</v>
       </c>
       <c r="H21" s="0" t="inlineStr">
         <is>
-          <t>哥布林x10</t>
+          <t>骷髅x10</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="n">
-        <v>70001</v>
+        <v>20011</v>
       </c>
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t>7001-7004</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C22" s="0" t="n">
         <v>1</v>
       </c>
       <c r="D22" s="0" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E22" s="0" t="inlineStr">
         <is>
-          <t>ui_research_38,Research</t>
-        </is>
-      </c>
-      <c r="F22" s="0" t="inlineStr">
-        <is>
-          <t>300700000,300700001|300700002|300700003|300700004|</t>
-        </is>
+          <t>ui_class_3</t>
+        </is>
+      </c>
+      <c r="F22" s="0" t="n">
+        <v>300210011</v>
       </c>
       <c r="G22" s="0" t="n">
-        <v>70001</v>
+        <v>20011</v>
       </c>
       <c r="H22" s="0" t="inlineStr">
         <is>
-          <t>兽人</t>
+          <t>骷髅战士x1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="n">
-        <v>70002</v>
+        <v>20012</v>
       </c>
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t>7001-7004</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C23" s="0" t="n">
         <v>5</v>
       </c>
       <c r="D23" s="0" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E23" s="0" t="inlineStr">
         <is>
-          <t>ui_research_38,Research</t>
+          <t>ui_class_3</t>
         </is>
       </c>
       <c r="F23" s="0" t="n">
-        <v>300700101</v>
+        <v>300210012</v>
       </c>
       <c r="G23" s="0" t="n">
-        <v>70002</v>
+        <v>20012</v>
       </c>
       <c r="H23" s="0" t="inlineStr">
         <is>
-          <t>兽人x5</t>
+          <t>骷髅战士x5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="n">
-        <v>70003</v>
+        <v>20013</v>
       </c>
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t>7001-7004</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C24" s="0" t="n">
         <v>10</v>
       </c>
       <c r="D24" s="0" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E24" s="0" t="inlineStr">
+        <is>
+          <t>ui_class_3</t>
+        </is>
+      </c>
+      <c r="F24" s="0" t="n">
+        <v>300210013</v>
+      </c>
+      <c r="G24" s="0" t="n">
+        <v>20013</v>
+      </c>
+      <c r="H24" s="0" t="inlineStr">
+        <is>
+          <t>骷髅战士x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>20021</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>100</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>ui_class_6</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>300210021</v>
+      </c>
+      <c r="G25" t="n">
+        <v>20021</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>骷髅投手x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>20022</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>5</v>
+      </c>
+      <c r="D26" t="n">
+        <v>500</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>ui_class_6</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>300210022</v>
+      </c>
+      <c r="G26" t="n">
+        <v>20022</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>骷髅投手x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>20023</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>10</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>ui_class_6</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>300210023</v>
+      </c>
+      <c r="G27" t="n">
+        <v>20023</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>骷髅投手x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>20031</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>100</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>ui_class_10</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>300210031</v>
+      </c>
+      <c r="G28" t="n">
+        <v>20031</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>骷髅魔法师（火）x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>20032</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>5</v>
+      </c>
+      <c r="D29" t="n">
+        <v>500</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>ui_class_10</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>300210032</v>
+      </c>
+      <c r="G29" t="n">
+        <v>20032</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>骷髅魔法师（火）x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>20033</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>10</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>ui_class_10</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>300210033</v>
+      </c>
+      <c r="G30" t="n">
+        <v>20033</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>骷髅魔法师（火）x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="12" customHeight="1" s="1">
+      <c r="A31" t="n">
+        <v>20041</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>100</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>ui_class_2</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>300210041</v>
+      </c>
+      <c r="G31" t="n">
+        <v>20041</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>骷髅魔法师（冰）x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="12" customHeight="1" s="1">
+      <c r="A32" t="n">
+        <v>20042</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>5</v>
+      </c>
+      <c r="D32" t="n">
+        <v>500</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>ui_class_2</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>300210042</v>
+      </c>
+      <c r="G32" t="n">
+        <v>20042</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>骷髅魔法师（冰）x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="12" customHeight="1" s="1">
+      <c r="A33" t="n">
+        <v>20043</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>10</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>ui_class_2</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>300210043</v>
+      </c>
+      <c r="G33" t="n">
+        <v>20043</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>骷髅魔法师（冰）x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="12" customHeight="1" s="1">
+      <c r="A34" t="n">
+        <v>30001</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>3001-3004</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>20</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>ui_research_37,Research</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>300300000,300300001|300300002|300300003|300300004|</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>30001</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>史莱姆</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="12" customHeight="1" s="1">
+      <c r="A35" t="n">
+        <v>30002</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>3001-3004</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>5</v>
+      </c>
+      <c r="D35" t="n">
         <v>200</v>
       </c>
-      <c r="E24" s="0" t="inlineStr">
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>ui_research_37,Research</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>300300101</v>
+      </c>
+      <c r="G35" t="n">
+        <v>30002</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>史莱姆x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="12" customHeight="1" s="1">
+      <c r="A36" t="n">
+        <v>30003</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>3001-3004</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>10</v>
+      </c>
+      <c r="D36" t="n">
+        <v>400</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>ui_research_37,Research</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>300300102</v>
+      </c>
+      <c r="G36" t="n">
+        <v>30003</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>史莱姆x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="12" customHeight="1" s="1">
+      <c r="A37" t="n">
+        <v>30011</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="n">
+        <v>200</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>ui_class_8</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>300310011</v>
+      </c>
+      <c r="G37" t="n">
+        <v>30011</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>守护史莱姆x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="12" customHeight="1" s="1">
+      <c r="A38" t="n">
+        <v>30012</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>5</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>ui_class_8</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>300310012</v>
+      </c>
+      <c r="G38" t="n">
+        <v>30012</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>守护史莱姆x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="12" customHeight="1" s="1">
+      <c r="A39" t="n">
+        <v>30013</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>10</v>
+      </c>
+      <c r="D39" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>ui_class_8</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>300310013</v>
+      </c>
+      <c r="G39" t="n">
+        <v>30013</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>守护史莱姆x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>30021</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>3002</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="n">
+        <v>200</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>ui_class_9</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>300310021</v>
+      </c>
+      <c r="G40" t="n">
+        <v>30021</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>自爆史莱姆x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>30022</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>3002</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>5</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>ui_class_9</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>300310022</v>
+      </c>
+      <c r="G41" t="n">
+        <v>30022</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>自爆史莱姆x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>30023</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>3002</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>10</v>
+      </c>
+      <c r="D42" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>ui_class_9</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>300310023</v>
+      </c>
+      <c r="G42" t="n">
+        <v>30023</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>自爆史莱姆x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30031</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>3003</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" t="n">
+        <v>200</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>ui_class_11</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>300310031</v>
+      </c>
+      <c r="G43" t="n">
+        <v>30031</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>烂泥史莱姆x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>30032</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>3003</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>5</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>ui_class_11</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>300310032</v>
+      </c>
+      <c r="G44" t="n">
+        <v>30032</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>烂泥史莱姆x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>30033</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>3003</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>10</v>
+      </c>
+      <c r="D45" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>ui_class_11</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>300310033</v>
+      </c>
+      <c r="G45" t="n">
+        <v>30033</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>烂泥史莱姆x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>30041</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>3004</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="n">
+        <v>200</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>ui_class_12</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>300310041</v>
+      </c>
+      <c r="G46" t="n">
+        <v>30041</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>毒液史莱姆x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>30042</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>3004</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>5</v>
+      </c>
+      <c r="D47" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>ui_class_12</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>300310042</v>
+      </c>
+      <c r="G47" t="n">
+        <v>30042</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>毒液史莱姆x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>30043</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>3004</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>10</v>
+      </c>
+      <c r="D48" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>ui_class_12</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>300310043</v>
+      </c>
+      <c r="G48" t="n">
+        <v>30043</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>毒液史莱姆x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>40001</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>4001-4005</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="n">
+        <v>20</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>ui_research_41,Research</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>300400000,300400001|300400002|300400003|300400004|300400005|</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>40001</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>魅魔</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>40002</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>4001-4005</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>5</v>
+      </c>
+      <c r="D50" t="n">
+        <v>100</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>ui_research_41,Research</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>300400101</v>
+      </c>
+      <c r="G50" t="n">
+        <v>40002</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>魅魔x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>40003</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>4001-4005</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>10</v>
+      </c>
+      <c r="D51" t="n">
+        <v>200</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>ui_research_41,Research</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>300400102</v>
+      </c>
+      <c r="G51" t="n">
+        <v>40003</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>魅魔x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>40011</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>4001</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="n">
+        <v>200</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>ui_class_3</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>300410011</v>
+      </c>
+      <c r="G52" t="n">
+        <v>40011</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>战之魅魔x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>40012</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>4001</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>5</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>ui_class_3</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>300410012</v>
+      </c>
+      <c r="G53" t="n">
+        <v>40012</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>战之魅魔x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>40013</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>4001</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>10</v>
+      </c>
+      <c r="D54" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>ui_class_3</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>300410013</v>
+      </c>
+      <c r="G54" t="n">
+        <v>40013</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>战之魅魔x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>40021</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>4002</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" t="n">
+        <v>200</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>ui_class_14</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>300410021</v>
+      </c>
+      <c r="G55" t="n">
+        <v>40021</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>愈之魅魔x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>40022</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>4002</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>5</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>ui_class_14</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>300410022</v>
+      </c>
+      <c r="G56" t="n">
+        <v>40022</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>愈之魅魔x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>40023</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>4002</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>10</v>
+      </c>
+      <c r="D57" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>ui_class_14</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>300410023</v>
+      </c>
+      <c r="G57" t="n">
+        <v>40023</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>愈之魅魔x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>40031</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>4003</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="n">
+        <v>200</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>ui_class_13</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>300410031</v>
+      </c>
+      <c r="G58" t="n">
+        <v>40031</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>惑之魅魔x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>40032</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>4003</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>5</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>ui_class_13</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>300410032</v>
+      </c>
+      <c r="G59" t="n">
+        <v>40032</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>惑之魅魔x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>40033</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>4003</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>10</v>
+      </c>
+      <c r="D60" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>ui_class_13</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>300410033</v>
+      </c>
+      <c r="G60" t="n">
+        <v>40033</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>惑之魅魔x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>40041</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>4004</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" t="n">
+        <v>200</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>ui_class_15</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>300410041</v>
+      </c>
+      <c r="G61" t="n">
+        <v>40041</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>奥之魅魔x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>40042</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>4004</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>5</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>ui_class_15</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>300410042</v>
+      </c>
+      <c r="G62" t="n">
+        <v>40042</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>奥之魅魔x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>40043</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>4004</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>10</v>
+      </c>
+      <c r="D63" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>ui_class_15</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>300410043</v>
+      </c>
+      <c r="G63" t="n">
+        <v>40043</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>奥之魅魔x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>40051</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>4005</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" t="n">
+        <v>200</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>ui_class_16</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>300410051</v>
+      </c>
+      <c r="G64" t="n">
+        <v>40051</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>盾之魅魔x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>40052</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>4005</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>5</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>ui_class_16</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>300410052</v>
+      </c>
+      <c r="G65" t="n">
+        <v>40052</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>盾之魅魔x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>40053</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>4005</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>10</v>
+      </c>
+      <c r="D66" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>ui_class_16</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>300410053</v>
+      </c>
+      <c r="G66" t="n">
+        <v>40053</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>盾之魅魔x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>50001</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>5001-5004</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" t="n">
+        <v>20</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>ui_research_40,Research</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>300500000,300500001|300500002|300500003|300500004|</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>50001</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>牛头人</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>50002</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>5001-5004</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>5</v>
+      </c>
+      <c r="D68" t="n">
+        <v>100</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>ui_research_40,Research</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>300500101</v>
+      </c>
+      <c r="G68" t="n">
+        <v>50002</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>牛头人x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>50003</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>5001-5004</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>10</v>
+      </c>
+      <c r="D69" t="n">
+        <v>200</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>ui_research_40,Research</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>300500102</v>
+      </c>
+      <c r="G69" t="n">
+        <v>50003</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>牛头人x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>50011</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" t="n">
+        <v>200</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>ui_class_3</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>300510011</v>
+      </c>
+      <c r="G70" t="n">
+        <v>50011</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>牛头人战士x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>50012</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>5</v>
+      </c>
+      <c r="D71" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>ui_class_3</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>300510012</v>
+      </c>
+      <c r="G71" t="n">
+        <v>50012</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>牛头人战士x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>50013</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>10</v>
+      </c>
+      <c r="D72" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>ui_class_3</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>300510013</v>
+      </c>
+      <c r="G72" t="n">
+        <v>50013</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>牛头人战士x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>50021</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>5002</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" t="n">
+        <v>200</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>ui_class_6</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>300510021</v>
+      </c>
+      <c r="G73" t="n">
+        <v>50021</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>牛头人投手x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>50022</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>5002</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>5</v>
+      </c>
+      <c r="D74" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>ui_class_6</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>300510022</v>
+      </c>
+      <c r="G74" t="n">
+        <v>50022</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>牛头人投手x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>50023</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>5002</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>10</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>ui_class_6</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>300510023</v>
+      </c>
+      <c r="G75" t="n">
+        <v>50023</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>牛头人投手x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>50031</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>5003</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" t="n">
+        <v>200</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>ui_class_10</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>300510031</v>
+      </c>
+      <c r="G76" t="n">
+        <v>50031</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>牛头人魔法师（火）x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>50032</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>5003</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>5</v>
+      </c>
+      <c r="D77" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>ui_class_10</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>300510032</v>
+      </c>
+      <c r="G77" t="n">
+        <v>50032</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>牛头人魔法师（火）x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>50033</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>5003</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>10</v>
+      </c>
+      <c r="D78" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>ui_class_10</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>300510033</v>
+      </c>
+      <c r="G78" t="n">
+        <v>50033</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>牛头人魔法师（火）x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>50041</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>5004</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" t="n">
+        <v>200</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>ui_class_2</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>300510041</v>
+      </c>
+      <c r="G79" t="n">
+        <v>50041</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>牛头人魔法师（冰）x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>50042</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>5004</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>5</v>
+      </c>
+      <c r="D80" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>ui_class_2</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>300510042</v>
+      </c>
+      <c r="G80" t="n">
+        <v>50042</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>牛头人魔法师（冰）x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>50043</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>5004</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>10</v>
+      </c>
+      <c r="D81" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>ui_class_2</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>300510043</v>
+      </c>
+      <c r="G81" t="n">
+        <v>50043</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>牛头人魔法师（冰）x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>60001</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>6001-6005</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" t="n">
+        <v>20</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>ui_research_39,Research</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>300600000,300600001|300600002|300600003|300600004|300600005|</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>60001</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>哥布林</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>60002</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>6001-6005</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>5</v>
+      </c>
+      <c r="D83" t="n">
+        <v>100</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>ui_research_39,Research</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>300600101</v>
+      </c>
+      <c r="G83" t="n">
+        <v>60002</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>哥布林x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>60003</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>6001-6005</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>10</v>
+      </c>
+      <c r="D84" t="n">
+        <v>200</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>ui_research_39,Research</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>300600102</v>
+      </c>
+      <c r="G84" t="n">
+        <v>60003</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>哥布林x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>60011</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>6001</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" t="n">
+        <v>200</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>ui_class_1</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>300610011</v>
+      </c>
+      <c r="G85" t="n">
+        <v>60011</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>哥布林刺客x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>60012</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>6001</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>5</v>
+      </c>
+      <c r="D86" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>ui_class_1</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>300610012</v>
+      </c>
+      <c r="G86" t="n">
+        <v>60012</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>哥布林刺客x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>60013</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>6001</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>10</v>
+      </c>
+      <c r="D87" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>ui_class_1</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>300610013</v>
+      </c>
+      <c r="G87" t="n">
+        <v>60013</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>哥布林刺客x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>60021</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>6002</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>1</v>
+      </c>
+      <c r="D88" t="n">
+        <v>200</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>ui_class_6</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>300610021</v>
+      </c>
+      <c r="G88" t="n">
+        <v>60021</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>哥布林弓箭手x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>60022</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>6002</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>5</v>
+      </c>
+      <c r="D89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>ui_class_6</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>300610022</v>
+      </c>
+      <c r="G89" t="n">
+        <v>60022</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>哥布林弓箭手x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>60023</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>6002</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>10</v>
+      </c>
+      <c r="D90" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>ui_class_6</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>300610023</v>
+      </c>
+      <c r="G90" t="n">
+        <v>60023</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>哥布林弓箭手x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>60031</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>6003</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>1</v>
+      </c>
+      <c r="D91" t="n">
+        <v>200</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>ui_class_9</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>300610031</v>
+      </c>
+      <c r="G91" t="n">
+        <v>60031</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>哥布林敢死队x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>60032</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>6003</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>5</v>
+      </c>
+      <c r="D92" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>ui_class_9</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>300610032</v>
+      </c>
+      <c r="G92" t="n">
+        <v>60032</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>哥布林敢死队x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>60033</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>6003</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>10</v>
+      </c>
+      <c r="D93" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>ui_class_9</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>300610033</v>
+      </c>
+      <c r="G93" t="n">
+        <v>60033</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>哥布林敢死队x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>60041</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>6004</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>1</v>
+      </c>
+      <c r="D94" t="n">
+        <v>200</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>ui_class_10</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>300610041</v>
+      </c>
+      <c r="G94" t="n">
+        <v>60041</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>哥布林魔法师（火）x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>60042</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>6004</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>5</v>
+      </c>
+      <c r="D95" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>ui_class_10</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>300610042</v>
+      </c>
+      <c r="G95" t="n">
+        <v>60042</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>哥布林魔法师（火）x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>60043</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>6004</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>10</v>
+      </c>
+      <c r="D96" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>ui_class_10</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>300610043</v>
+      </c>
+      <c r="G96" t="n">
+        <v>60043</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>哥布林魔法师（火）x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>60051</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>6005</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>1</v>
+      </c>
+      <c r="D97" t="n">
+        <v>200</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>ui_class_2</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>300610051</v>
+      </c>
+      <c r="G97" t="n">
+        <v>60051</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>哥布林魔法师（冰）x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>60052</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>6005</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>5</v>
+      </c>
+      <c r="D98" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>ui_class_2</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>300610052</v>
+      </c>
+      <c r="G98" t="n">
+        <v>60052</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>哥布林魔法师（冰）x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>60053</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>6005</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>10</v>
+      </c>
+      <c r="D99" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>ui_class_2</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>300610053</v>
+      </c>
+      <c r="G99" t="n">
+        <v>60053</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>哥布林魔法师（冰）x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>70001</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>7001-7004</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>1</v>
+      </c>
+      <c r="D100" t="n">
+        <v>20</v>
+      </c>
+      <c r="E100" t="inlineStr">
         <is>
           <t>ui_research_38,Research</t>
         </is>
       </c>
-      <c r="F24" s="0" t="n">
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>300700000,300700001|300700002|300700003|300700004|</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>70001</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>兽人</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>70002</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>7001-7004</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>5</v>
+      </c>
+      <c r="D101" t="n">
+        <v>100</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>ui_research_38,Research</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>300700101</v>
+      </c>
+      <c r="G101" t="n">
+        <v>70002</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>兽人x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>70003</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>7001-7004</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>10</v>
+      </c>
+      <c r="D102" t="n">
+        <v>200</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>ui_research_38,Research</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
         <v>300700102</v>
       </c>
-      <c r="G24" s="0" t="n">
+      <c r="G102" t="n">
         <v>70003</v>
       </c>
-      <c r="H24" s="0" t="inlineStr">
+      <c r="H102" t="inlineStr">
         <is>
           <t>兽人x10</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="12" customHeight="1" s="1"/>
-    <row r="32" ht="12" customHeight="1" s="1"/>
-    <row r="33" ht="12" customHeight="1" s="1"/>
-    <row r="34" ht="12" customHeight="1" s="1"/>
-    <row r="35" ht="12" customHeight="1" s="1"/>
-    <row r="36" ht="12" customHeight="1" s="1"/>
-    <row r="37" ht="12" customHeight="1" s="1"/>
-    <row r="38" ht="12" customHeight="1" s="1"/>
-    <row r="39" ht="12" customHeight="1" s="1"/>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>70011</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>7001</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>1</v>
+      </c>
+      <c r="D103" t="n">
+        <v>200</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>ui_class_3</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>300710011</v>
+      </c>
+      <c r="G103" t="n">
+        <v>70011</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>兽人战士x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>70012</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>7001</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>5</v>
+      </c>
+      <c r="D104" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>ui_class_3</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>300710012</v>
+      </c>
+      <c r="G104" t="n">
+        <v>70012</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>兽人战士x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>70013</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>7001</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>10</v>
+      </c>
+      <c r="D105" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>ui_class_3</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>300710013</v>
+      </c>
+      <c r="G105" t="n">
+        <v>70013</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>兽人战士x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>70021</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>7002</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>1</v>
+      </c>
+      <c r="D106" t="n">
+        <v>200</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>ui_class_6</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>300710021</v>
+      </c>
+      <c r="G106" t="n">
+        <v>70021</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>兽人弓箭手x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>70022</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>7002</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>5</v>
+      </c>
+      <c r="D107" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>ui_class_6</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>300710022</v>
+      </c>
+      <c r="G107" t="n">
+        <v>70022</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>兽人弓箭手x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>70023</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>7002</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>10</v>
+      </c>
+      <c r="D108" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>ui_class_6</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>300710023</v>
+      </c>
+      <c r="G108" t="n">
+        <v>70023</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>兽人弓箭手x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>70031</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>7003</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>1</v>
+      </c>
+      <c r="D109" t="n">
+        <v>200</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>ui_class_10</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>300710031</v>
+      </c>
+      <c r="G109" t="n">
+        <v>70031</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>兽人魔法师（火）x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>70032</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>7003</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>5</v>
+      </c>
+      <c r="D110" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>ui_class_10</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>300710032</v>
+      </c>
+      <c r="G110" t="n">
+        <v>70032</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>兽人魔法师（火）x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>70033</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>7003</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>10</v>
+      </c>
+      <c r="D111" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>ui_class_10</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>300710033</v>
+      </c>
+      <c r="G111" t="n">
+        <v>70033</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>兽人魔法师（火）x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>70041</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>7004</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>1</v>
+      </c>
+      <c r="D112" t="n">
+        <v>200</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>ui_class_2</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>300710041</v>
+      </c>
+      <c r="G112" t="n">
+        <v>70041</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>兽人魔法师（冰）x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>70042</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>7004</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>5</v>
+      </c>
+      <c r="D113" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>ui_class_2</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>300710042</v>
+      </c>
+      <c r="G113" t="n">
+        <v>70042</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>兽人魔法师（冰）x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>70043</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>7004</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>10</v>
+      </c>
+      <c r="D114" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>ui_class_2</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>300710043</v>
+      </c>
+      <c r="G114" t="n">
+        <v>70043</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>兽人魔法师（冰）x10</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
